--- a/back-end/mkd_works_service/api/templates/year_act/mkd_services_year_act_template.xlsx
+++ b/back-end/mkd_works_service/api/templates/year_act/mkd_services_year_act_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Housing Company Services(HCS)\back-end\mkd_works_service\api\templates\year_act\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A380884B-6305-4160-AEFA-12160DFBC061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58767C2B-DDC9-4571-8BB6-C177972163A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -61,181 +61,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>User24</author>
-  </authors>
-  <commentList>
-    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>договор с УК "ЖЭК-Максимум"
-0.69 р. 1 полугодие
-0.77 р. 2 полугодие</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>8400 справка январь 23
-3200р справка март23
-2500 справка декабрь 23
-4470р см 30/2023</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">49510.63 з/плата по факту
-15199.76 налоги на ФОТ
-2862 руб. материалы
-Итого 67572.39
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">12000 з/плата по факту
-3684 налоги на ФОТ
-3750 руб. уборка снега
-Итого 67572.39
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
-      <text/>
-    </comment>
-    <comment ref="B23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>см 2/2023 от 28.04.2023г</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>8233р см 3/2023
-1600р. *3 ч= 4800 р</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">см 12/2023 от 25.05.2023
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>1297р. см 6/2023 от 28.02
-17435р. См 25/2023 от 16.10.2023
-3360р. Транспортные расходы 2ч</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>40267.00 см 5/2023 от 30.09.2023
-2624.00 см 6а/2023 от 29.09.2023</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>см 28/2023 от 18.12.2023</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
   <si>
     <t xml:space="preserve">         АКТ №__1____</t>
   </si>
@@ -458,35 +285,8 @@
     <t xml:space="preserve">Председатель Совета дома                  ___________________________ Молчанов М.В.     </t>
   </si>
   <si>
-    <t>г. Трехгорный                                                                                                                                                                                                             21 февраля 2024 г.</t>
-  </si>
-  <si>
-    <t>демонтаж сараек и вывоз мусора 60 922.00</t>
-  </si>
-  <si>
-    <t>замена межтамбурной двери в 3 п. 52 992.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ремонт водосточной системы 22 092.00 </t>
-  </si>
-  <si>
-    <t>сантехнические работы 42 891.00</t>
-  </si>
-  <si>
-    <t>электромонтажные работы 7 537.00</t>
-  </si>
-  <si>
-    <t>очистка(ремонт) карниза 13033.00</t>
-  </si>
-  <si>
-    <t>ремонт цоколя 35 187.00</t>
-  </si>
-  <si>
-    <t>2. Всего за период с 01 января 2023 года по 31 декабря 2023 года выполнено работ (оказано услуг) на общую сумму 568 165.54 рубл.</t>
-  </si>
-  <si>
     <r>
-      <t>многоквартирном доме № {{</t>
+      <t xml:space="preserve">многоквартирном доме № </t>
     </r>
     <r>
       <rPr>
@@ -497,17 +297,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>house_number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>}}</t>
+      <t>{{street_number}}</t>
     </r>
     <r>
       <rPr>
@@ -528,18 +318,67 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve"> {{street_name}}</t>
+      <t xml:space="preserve"> </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>{{street}}</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">         АКТ № {{act_num}}</t>
+  </si>
+  <si>
+    <t>г. Трехгорный                                                                                                                                                                                                           {{act_date}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Собственники помещений в многоквартирном доме, расположенном по адресу: ул. {{street}}, дом № {{street_number}}, именуемые  в дальнейшем « Заказчик»,</t>
+  </si>
+  <si>
+    <t>именуемый в дальнейшем « Исполнитель», в лице генерального директора {{company_director}},  с другой стороны, совместно именуемые "Стороны",</t>
+  </si>
+  <si>
+    <r>
+      <t>выполненные работы по содержанию и текущему ремонту общего имущества в многоквартирном доме № {{street_number}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>, расположенном по ул. {{street}}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>в лице  председателя Совета дома {{house_director}}, являющегося собственником квартиры № {{house_director_appartment}} с одной стороны, и {{company_name}},</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,19 +423,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -625,6 +451,14 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -766,104 +600,101 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -896,24 +727,23 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,104 +1098,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -1401,13 +1231,13 @@
       <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E13" s="6">
@@ -1417,32 +1247,32 @@
         <f>F11*E13*12</f>
         <v>77189.111999999994</v>
       </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="21"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2.1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="6">
@@ -1452,19 +1282,19 @@
         <f>E15*F11*12</f>
         <v>74070.36</v>
       </c>
-      <c r="G15" s="21"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="6">
@@ -1474,19 +1304,19 @@
         <f>E16*F11*12</f>
         <v>72121.14</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="6">
@@ -1496,19 +1326,19 @@
         <f>F11*E17*12</f>
         <v>26899.235999999997</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2.4</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="6">
@@ -1518,148 +1348,148 @@
         <f>E18*F11*6</f>
         <v>31577.364000000001</v>
       </c>
-      <c r="G18" s="21"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="38">
         <v>1.89</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="38">
         <f>F11*E19*12</f>
         <v>73680.516000000003</v>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="43">
         <v>0.21</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="43">
         <v>4240.72</v>
       </c>
-      <c r="G20" s="21"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="24">
         <v>12.634</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <v>492508.58</v>
       </c>
-      <c r="G21" s="21"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="21"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="21"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="21"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="21"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="21"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="34"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="15"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
@@ -1678,50 +1508,50 @@
       <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+      <c r="A31" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
+      <c r="A35" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
@@ -1732,14 +1562,14 @@
       <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="47" t="s">
+      <c r="A37" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
@@ -1750,7 +1580,7 @@
       <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B39" s="16"/>
@@ -1760,7 +1590,7 @@
       <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="45"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -1768,7 +1598,7 @@
       <c r="F40" s="16"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="16"/>
@@ -1786,14 +1616,14 @@
       <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="47" t="s">
+      <c r="A43" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
@@ -1804,14 +1634,14 @@
       <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="47" t="s">
+      <c r="A45" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
@@ -1822,24 +1652,24 @@
       <c r="F46" s="3"/>
     </row>
     <row r="47" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="47" t="s">
+      <c r="A48" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
@@ -1883,17 +1713,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="C14:F14"/>
@@ -1904,6 +1723,17 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -1912,11 +1742,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" customWidth="1"/>
@@ -1927,117 +1757,115 @@
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="2">
-        <v>3248.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
@@ -2057,533 +1885,45 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.37</v>
-      </c>
-      <c r="F13" s="6">
-        <f>F11*E13*12</f>
-        <v>53408.627999999997</v>
-      </c>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="46"/>
-    </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="F15" s="6">
-        <f>E15*F11*12</f>
-        <v>74070.36</v>
-      </c>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="F16" s="6">
-        <f>E16*F11*12</f>
-        <v>72121.14</v>
-      </c>
-      <c r="G16" s="21"/>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.73</v>
-      </c>
-      <c r="F17" s="6">
-        <f>F11*E17*12</f>
-        <v>28458.612000000001</v>
-      </c>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="F18" s="6">
-        <f>E18*F11*6</f>
-        <v>18517.59</v>
-      </c>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="39">
-        <v>1.73</v>
-      </c>
-      <c r="F19" s="39">
-        <f>F11*E19*12</f>
-        <v>67443.011999999988</v>
-      </c>
-      <c r="G19" s="21"/>
-    </row>
-    <row r="20" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="F20" s="39">
-        <f>F11*E20*12</f>
-        <v>19492.199999999997</v>
-      </c>
-      <c r="G20" s="21"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="25">
-        <v>6.02</v>
-      </c>
-      <c r="F21" s="26">
-        <v>234654</v>
-      </c>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="21"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="21"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="21"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="21"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
-      <c r="B28" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="21"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="21"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="21"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="45"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="45"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-    </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="45"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-    </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-    </row>
-    <row r="50" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A33:F33"/>
+  <mergeCells count="10">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/back-end/mkd_works_service/api/templates/year_act/mkd_services_year_act_template.xlsx
+++ b/back-end/mkd_works_service/api/templates/year_act/mkd_services_year_act_template.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Projects\Housing Company Services(HCS)\back-end\mkd_works_service\api\templates\year_act\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01195FF5-5DBB-4450-B892-BD9C629DAF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16978A7E-0801-48C4-A448-BA2C2A29ED4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t xml:space="preserve">приемки оказанных услуг и (или) выполненных работ по содержанию и текущему ремонту общего имущества в </t>
   </si>
@@ -148,12 +149,118 @@
   <si>
     <t>в лице  председателя Совета дома {{house_director}}, являющегося собственником квартиры № {{house_director_appartment}} с одной стороны, и {{company_name}},</t>
   </si>
+  <si>
+    <t>УТВЕРЖДЕНО приказом Министерства строительства и жилищно- коммунального хозяйства Российской Федерации от 26.10.2015 N 761/пр</t>
+  </si>
+  <si>
+    <t>Акт № {{act_num}}</t>
+  </si>
+  <si>
+    <t>приемки оказанных услуг и (или) выполненных работ по содержанию и</t>
+  </si>
+  <si>
+    <t>текущему ремонту общего имущества в многоквартирном доме</t>
+  </si>
+  <si>
+    <t>Г. Трехгорный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        именуемые в дальнейшем "Заказчик", в лице {{ house_director }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        являющегося собственником квартиры № {{house_director_appartment}}, находящейся в</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        данном многоквартирном доме, действующего на основании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Собственники помещений в многоквартирном доме, расположенном по адресу:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        456080 Челябинская область, г. Трехгорный, ул. {{street}}, д. {{street_number}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        {{ collective_direct_or_deliver_num }}, с одной стороны,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        и  {{company_name}}, именуемый  в дальнейшем "Исполнитель", в лице </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        генерального директора {{company_director}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        действующего на основании  Устава, с другой стороны, совместно именуемые "Стороны", составили настоящий Акт о 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        нижеследующем:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            1. Исполнителем предъявлены к приемке следующие оказанные на основании договора управления многоквартирным домом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       или договора оказания услуг по содержанию и (или) выполнению работ по ремонту общего имущества в многоквартирном доме</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       либо договора подряда по выполнению работ по ремонту общего имущества в многоквартирном доме (указать нужное)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{act_date}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       выполненные работы по содержанию и текущему ремонту общего имущества в многоквартирном доме № {{street_number}},</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       №   _   от "       "       г. (далее - "Договор") услуги и (или)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       расположенном по адресу: г. Трехгорный, ул. {{ street }}</t>
+  </si>
+  <si>
+    <t>Периодичность/количественн ый показатель выполненной работы (оказанной услуги)</t>
+  </si>
+  <si>
+    <t>Единица измерения работы (услуги)</t>
+  </si>
+  <si>
+    <t>Стоимость/сметна я стоимость выполненной работы (оказанной услуги) за месяц</t>
+  </si>
+  <si>
+    <t>Цена выполненной работы (оказанной услуги), в рублях</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        {{ all_work_sum }} руб.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         4. Претензий по выполнению условий Договора Стороны друг к другу не имеют. Настоящий Акт составлен в</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       2 экземплярах, имеющих одинаковую юридическую силу, по одному для каждой из Сторон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         3. Работы (услуги) выполнены (оказаны) полностью, в установленные сроки, с надлежащим качеством. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">         2. Всего за период с {{ start_work_date }} по {{ end_work_date }} выполнено работ (оказано услуг) на общую сумму</t>
+  </si>
+  <si>
+    <t>Подписи Сторон:</t>
+  </si>
+  <si>
+    <t>(подпись)</t>
+  </si>
+  <si>
+    <t>Исполнитель -              Генеральный директор  {{company_director}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказчик -                     </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +307,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -236,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -249,10 +363,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -607,104 +750,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -760,18 +903,414 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC7D1CE-6879-4716-A847-0AFCA559B6AB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="58.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>